--- a/backend/_data_list/users.xlsx
+++ b/backend/_data_list/users.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Telegram_Project\OrangeFlow_Dev\_data_list\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-26.04\home\neelima\projects\Orange-Flow-Next-Js\backend\_data_list\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7100DAD-7410-414D-896E-D236D21ACD80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F248ED3-8E66-461A-A578-18B672D29EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{BB0F9CCB-0FBE-4AFF-BD3B-D4E64BAEDA77}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BB0F9CCB-0FBE-4AFF-BD3B-D4E64BAEDA77}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="82">
   <si>
     <t xml:space="preserve"> TELEGRAM_ID</t>
   </si>
@@ -153,13 +153,145 @@
   </si>
   <si>
     <t>Sabbir Ahmed Bappy</t>
+  </si>
+  <si>
+    <t>USERNAME</t>
+  </si>
+  <si>
+    <t>PASSWORD</t>
+  </si>
+  <si>
+    <t>EMAIL</t>
+  </si>
+  <si>
+    <t>user1</t>
+  </si>
+  <si>
+    <t>user2</t>
+  </si>
+  <si>
+    <t>user3</t>
+  </si>
+  <si>
+    <t>user4</t>
+  </si>
+  <si>
+    <t>user5</t>
+  </si>
+  <si>
+    <t>user6</t>
+  </si>
+  <si>
+    <t>user7</t>
+  </si>
+  <si>
+    <t>user8</t>
+  </si>
+  <si>
+    <t>user9</t>
+  </si>
+  <si>
+    <t>user10</t>
+  </si>
+  <si>
+    <t>user11</t>
+  </si>
+  <si>
+    <t>user12</t>
+  </si>
+  <si>
+    <t>user13</t>
+  </si>
+  <si>
+    <t>user14</t>
+  </si>
+  <si>
+    <t>user15</t>
+  </si>
+  <si>
+    <t>user16</t>
+  </si>
+  <si>
+    <t>user17</t>
+  </si>
+  <si>
+    <t>user18</t>
+  </si>
+  <si>
+    <t>user19</t>
+  </si>
+  <si>
+    <t>user20</t>
+  </si>
+  <si>
+    <t>user1@gmail.com</t>
+  </si>
+  <si>
+    <t>user2@gmail.com</t>
+  </si>
+  <si>
+    <t>user3@gmail.com</t>
+  </si>
+  <si>
+    <t>user4@gmail.com</t>
+  </si>
+  <si>
+    <t>user5@gmail.com</t>
+  </si>
+  <si>
+    <t>user6@gmail.com</t>
+  </si>
+  <si>
+    <t>user7@gmail.com</t>
+  </si>
+  <si>
+    <t>user8@gmail.com</t>
+  </si>
+  <si>
+    <t>user9@gmail.com</t>
+  </si>
+  <si>
+    <t>user10@gmail.com</t>
+  </si>
+  <si>
+    <t>user11@gmail.com</t>
+  </si>
+  <si>
+    <t>user12@gmail.com</t>
+  </si>
+  <si>
+    <t>user13@gmail.com</t>
+  </si>
+  <si>
+    <t>user14@gmail.com</t>
+  </si>
+  <si>
+    <t>user15@gmail.com</t>
+  </si>
+  <si>
+    <t>user16@gmail.com</t>
+  </si>
+  <si>
+    <t>user17@gmail.com</t>
+  </si>
+  <si>
+    <t>user18@gmail.com</t>
+  </si>
+  <si>
+    <t>user19@gmail.com</t>
+  </si>
+  <si>
+    <t>user20@gmail.com</t>
+  </si>
+  <si>
+    <t>Password123</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -169,6 +301,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -191,14 +331,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -531,18 +674,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B226F8CE-143F-43E3-8E7D-9AF252188EC1}">
-  <dimension ref="A1:F25"/>
-  <sheetFormatPr defaultColWidth="13.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I25"/>
+  <sheetFormatPr defaultColWidth="13.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -550,429 +696,618 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>21</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>8704561358</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2">
         <v>1917747555</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>18</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>32</v>
       </c>
-      <c r="F2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>8759226993</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E3">
         <v>1918537111</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>32</v>
       </c>
-      <c r="F3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H3" t="s">
+        <v>81</v>
+      </c>
+      <c r="I3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>8474847602</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4">
         <v>1911229913</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
         <v>34</v>
       </c>
-      <c r="F4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H4" t="s">
+        <v>81</v>
+      </c>
+      <c r="I4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>8217920077</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" s="1">
         <v>1912317878</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>6</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
         <v>35</v>
       </c>
-      <c r="F5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H5" t="s">
+        <v>81</v>
+      </c>
+      <c r="I5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>8251541258</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="1">
         <v>1911626293</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
         <v>6</v>
       </c>
-      <c r="E6" t="s">
+      <c r="G6" t="s">
         <v>35</v>
       </c>
-      <c r="F6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H6" t="s">
+        <v>81</v>
+      </c>
+      <c r="I6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6857806283</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="1">
         <v>1831949395</v>
       </c>
-      <c r="D7" t="s">
+      <c r="F7" t="s">
         <v>14</v>
       </c>
-      <c r="E7" t="s">
+      <c r="G7" t="s">
         <v>31</v>
       </c>
-      <c r="F7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>8434757540</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" s="1">
         <v>1924303333</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>14</v>
       </c>
-      <c r="E8" t="s">
+      <c r="G8" t="s">
         <v>31</v>
       </c>
-      <c r="F8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7891698602</v>
       </c>
       <c r="B9" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E9" s="1">
         <v>1620502971</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
         <v>14</v>
       </c>
-      <c r="E9" t="s">
+      <c r="G9" t="s">
         <v>31</v>
       </c>
-      <c r="F9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H9" t="s">
+        <v>81</v>
+      </c>
+      <c r="I9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8681308050</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="1">
         <v>1911916176</v>
       </c>
-      <c r="D10" t="s">
+      <c r="F10" t="s">
         <v>14</v>
       </c>
-      <c r="E10" t="s">
+      <c r="G10" t="s">
         <v>31</v>
       </c>
-      <c r="F10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H10" t="s">
+        <v>81</v>
+      </c>
+      <c r="I10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>6287137090</v>
       </c>
       <c r="B11" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" s="1">
         <v>1976466262</v>
       </c>
-      <c r="D11" t="s">
+      <c r="F11" t="s">
         <v>12</v>
       </c>
-      <c r="E11" t="s">
+      <c r="G11" t="s">
         <v>33</v>
       </c>
-      <c r="F11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H11" t="s">
+        <v>81</v>
+      </c>
+      <c r="I11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>6594315783</v>
       </c>
       <c r="B12" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" s="1">
         <v>1813862410</v>
       </c>
-      <c r="D12" t="s">
+      <c r="F12" t="s">
         <v>14</v>
       </c>
-      <c r="E12" t="s">
+      <c r="G12" t="s">
         <v>31</v>
       </c>
-      <c r="F12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H12" t="s">
+        <v>81</v>
+      </c>
+      <c r="I12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>7524803812</v>
       </c>
       <c r="B13" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="1">
         <v>1642536878</v>
       </c>
-      <c r="D13" t="s">
+      <c r="F13" t="s">
         <v>14</v>
       </c>
-      <c r="E13" t="s">
+      <c r="G13" t="s">
         <v>31</v>
       </c>
-      <c r="F13" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H13" t="s">
+        <v>81</v>
+      </c>
+      <c r="I13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>7479560514</v>
       </c>
       <c r="B14" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E14" s="1">
         <v>1775222954</v>
       </c>
-      <c r="D14" t="s">
+      <c r="F14" t="s">
         <v>14</v>
       </c>
-      <c r="E14" t="s">
+      <c r="G14" t="s">
         <v>31</v>
       </c>
-      <c r="F14" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H14" t="s">
+        <v>81</v>
+      </c>
+      <c r="I14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>7224463249</v>
       </c>
       <c r="B15" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15" s="1">
         <v>1917509966</v>
       </c>
-      <c r="D15" t="s">
+      <c r="F15" t="s">
         <v>14</v>
       </c>
-      <c r="E15" t="s">
+      <c r="G15" t="s">
         <v>31</v>
       </c>
-      <c r="F15" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H15" t="s">
+        <v>81</v>
+      </c>
+      <c r="I15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>6519999519</v>
       </c>
       <c r="B16" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" s="1">
         <v>1997616187</v>
       </c>
-      <c r="D16" t="s">
+      <c r="F16" t="s">
         <v>14</v>
       </c>
-      <c r="E16" t="s">
+      <c r="G16" t="s">
         <v>31</v>
       </c>
-      <c r="F16" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H16" t="s">
+        <v>81</v>
+      </c>
+      <c r="I16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>7586404983</v>
       </c>
       <c r="B17" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E17" s="1">
         <v>1970772132</v>
       </c>
-      <c r="D17" t="s">
+      <c r="F17" t="s">
         <v>14</v>
       </c>
-      <c r="E17" t="s">
+      <c r="G17" t="s">
         <v>31</v>
       </c>
-      <c r="F17" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H17" t="s">
+        <v>81</v>
+      </c>
+      <c r="I17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>7713329612</v>
       </c>
       <c r="B18" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E18" s="1">
         <v>1325533299</v>
       </c>
-      <c r="D18" t="s">
+      <c r="F18" t="s">
         <v>30</v>
       </c>
-      <c r="E18" t="s">
+      <c r="G18" t="s">
         <v>33</v>
       </c>
-      <c r="F18" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H18" t="s">
+        <v>81</v>
+      </c>
+      <c r="I18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>8273936271</v>
       </c>
       <c r="B19" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="1">
         <v>1915343494</v>
       </c>
-      <c r="D19" t="s">
+      <c r="F19" t="s">
         <v>14</v>
       </c>
-      <c r="E19" t="s">
+      <c r="G19" t="s">
         <v>31</v>
       </c>
-      <c r="F19" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H19" t="s">
+        <v>81</v>
+      </c>
+      <c r="I19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>8980795758</v>
       </c>
       <c r="B20" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E20" s="1">
         <v>1407911493</v>
       </c>
-      <c r="D20" t="s">
+      <c r="F20" t="s">
         <v>30</v>
       </c>
-      <c r="E20" t="s">
+      <c r="G20" t="s">
         <v>33</v>
       </c>
-      <c r="F20" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H20" t="s">
+        <v>81</v>
+      </c>
+      <c r="I20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>6534313772</v>
       </c>
       <c r="B21" t="s">
         <v>37</v>
       </c>
-      <c r="C21">
+      <c r="C21" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E21">
         <v>1322159543</v>
       </c>
-      <c r="D21" t="s">
+      <c r="F21" t="s">
         <v>14</v>
       </c>
-      <c r="E21" t="s">
+      <c r="G21" t="s">
         <v>31</v>
       </c>
-      <c r="F21" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C22" s="1"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C23" s="1"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C24" s="1"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C25" s="1"/>
+      <c r="H21" t="s">
+        <v>81</v>
+      </c>
+      <c r="I21" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E22" s="1"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E23" s="1"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E24" s="1"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E25" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/backend/_data_list/users.xlsx
+++ b/backend/_data_list/users.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-26.04\home\neelima\projects\Orange-Flow-Next-Js\backend\_data_list\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Telegram_Project\Orange-Flow-Next-Js\backend\_data_list\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F248ED3-8E66-461A-A578-18B672D29EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C244B4-19DE-46B7-9C4E-96B4EBE94B21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BB0F9CCB-0FBE-4AFF-BD3B-D4E64BAEDA77}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BB0F9CCB-0FBE-4AFF-BD3B-D4E64BAEDA77}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -675,20 +675,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B226F8CE-143F-43E3-8E7D-9AF252188EC1}">
   <dimension ref="A1:I25"/>
-  <sheetFormatPr defaultColWidth="13.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="13.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -717,7 +717,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>8704561358</v>
       </c>
@@ -746,7 +746,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>8759226993</v>
       </c>
@@ -775,7 +775,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>8474847602</v>
       </c>
@@ -804,7 +804,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>8217920077</v>
       </c>
@@ -833,7 +833,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>8251541258</v>
       </c>
@@ -862,7 +862,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6857806283</v>
       </c>
@@ -891,7 +891,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>8434757540</v>
       </c>
@@ -920,7 +920,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7891698602</v>
       </c>
@@ -949,7 +949,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8681308050</v>
       </c>
@@ -978,7 +978,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>6287137090</v>
       </c>
@@ -1007,7 +1007,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>6594315783</v>
       </c>
@@ -1036,7 +1036,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>7524803812</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>7479560514</v>
       </c>
@@ -1094,7 +1094,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>7224463249</v>
       </c>
@@ -1123,7 +1123,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>6519999519</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>7586404983</v>
       </c>
@@ -1181,7 +1181,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>7713329612</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>8273936271</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>8980795758</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>6534313772</v>
       </c>
@@ -1297,16 +1297,16 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E22" s="1"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E24" s="1"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E25" s="1"/>
     </row>
   </sheetData>
